--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R6a17aca9eb7f4f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R1d24788abd9746ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -453,22 +453,6 @@
         <x:v>PowerShell入口返回0，数据库、SQL和三张CSV可读，派生表与报表一致</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="33" customHeight="1">
-      <x:c r="A19" s="5" t="str">
-        <x:v>可验证点</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="str">
-        <x:v>源表保全、曝光主键、污染原因、转化匹配、窗口状态、分组指标与跨产物对账</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="33" customHeight="1">
-      <x:c r="A20" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B20" s="5" t="str">
-        <x:v>CTE拆分、别名、索引名、注释、缩进、内部查询顺序、CSV必要引号和LF或CRLF行尾</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R1d24788abd9746ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rc8b4818d5af945fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,15 +346,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>脱敏在线实验事件库、归因策略和报表布局合同</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+        <x:v>本次在线实验事件库、归因策略和报表布局合同，用户标识已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取database、rules、starter和tools</x:v>
+        <x:v>重建实验曝光与转化归因，识别互斥实验污染，为实验分析师提供分组指标和窗口外转化明细</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -373,12 +373,12 @@
         <x:v>output/ab_attribution_review.db；output/rebuild_ab_attribution.sql；output/reports/cohort_metrics.csv；output/reports/sample_contamination.csv；output/reports/attribution_window.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>载入策略；归并曝光；识别污染；建立有效曝光；关联转化；裁决窗口；汇总指标；导出报表</x:v>
+        <x:v>用SQLite载入策略并归并曝光，识别实验族污染后建立有效曝光、关联转化、裁决归因窗口，再汇总指标并导出报表</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -439,18 +439,18 @@
     </x:row>
     <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>五张源表保持不变，正式处理只读本地脱敏材料</x:v>
+        <x:v>保留五张源表，只在输出库建立派生表；全部计算依据来自随包策略和报表合同</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>PowerShell入口返回0，数据库、SQL和三张CSV可读，派生表与报表一致</x:v>
+        <x:v>交付复核库、可执行SQL和三张CSV，派生表与报表采用同一套归因结果</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
